--- a/Result/03-07-25/NASDAQstock_03-07-25period252RS90.xlsx
+++ b/Result/03-07-25/NASDAQstock_03-07-25period252RS90.xlsx
@@ -42,14 +42,12 @@
     <font>
       <name val="新細明體"/>
       <charset val="136"/>
-      <family val="1"/>
       <color rgb="FFFF0000"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="新細明體"/>
       <charset val="136"/>
-      <family val="1"/>
       <color rgb="FF008000"/>
       <sz val="11"/>
     </font>
@@ -60,7 +58,7 @@
       <color rgb="00008000"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -95,6 +93,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -160,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -174,10 +178,11 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -824,7 +829,7 @@
       <c r="U2" t="n">
         <v>4.444444444444444</v>
       </c>
-      <c r="V2" s="11" t="b">
+      <c r="V2" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W2" t="b">
@@ -868,7 +873,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ2" s="12" t="inlineStr">
+      <c r="AJ2" s="13" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -897,7 +902,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>DASH</t>
         </is>
@@ -1003,7 +1008,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ3" s="12" t="inlineStr">
+      <c r="AJ3" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -1138,7 +1143,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ4" s="12" t="inlineStr">
+      <c r="AJ4" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -1167,7 +1172,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>CVNA</t>
         </is>
@@ -1273,7 +1278,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ5" s="12" t="inlineStr">
+      <c r="AJ5" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -1302,7 +1307,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>AS</t>
         </is>
@@ -1408,7 +1413,7 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AJ6" s="12" t="inlineStr">
+      <c r="AJ6" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -1437,7 +1442,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>GWRE</t>
         </is>
@@ -1543,7 +1548,7 @@
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="AJ7" s="12" t="inlineStr">
+      <c r="AJ7" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -1572,7 +1577,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>CRS</t>
         </is>
@@ -1678,7 +1683,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ8" s="12" t="inlineStr">
+      <c r="AJ8" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -1707,7 +1712,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>CRDO</t>
         </is>
@@ -1816,7 +1821,7 @@
           <t>2025-09-04</t>
         </is>
       </c>
-      <c r="AJ9" s="12" t="inlineStr">
+      <c r="AJ9" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -1951,7 +1956,7 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AJ10" s="14" t="inlineStr">
+      <c r="AJ10" s="15" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
@@ -1980,7 +1985,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>GFI</t>
         </is>
@@ -2086,7 +2091,7 @@
           <t>2025-08-22</t>
         </is>
       </c>
-      <c r="AJ11" s="14" t="inlineStr">
+      <c r="AJ11" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -2221,7 +2226,7 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AJ12" s="12" t="inlineStr">
+      <c r="AJ12" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -2356,7 +2361,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ13" s="14" t="inlineStr">
+      <c r="AJ13" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -2491,7 +2496,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ14" s="14" t="inlineStr">
+      <c r="AJ14" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -2520,7 +2525,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>AFRM</t>
         </is>
@@ -2632,7 +2637,7 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AJ15" s="12" t="inlineStr">
+      <c r="AJ15" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -2661,7 +2666,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>TOST</t>
         </is>
@@ -2769,7 +2774,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ16" s="12" t="inlineStr">
+      <c r="AJ16" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -2904,7 +2909,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ17" s="14" t="inlineStr">
+      <c r="AJ17" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -2933,7 +2938,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>RBRK</t>
         </is>
@@ -3039,7 +3044,7 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AJ18" s="12" t="inlineStr">
+      <c r="AJ18" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -3068,7 +3073,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>AU</t>
         </is>
@@ -3174,7 +3179,7 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AJ19" s="14" t="inlineStr">
+      <c r="AJ19" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -3203,7 +3208,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>AEM</t>
         </is>
@@ -3309,7 +3314,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ20" s="14" t="inlineStr">
+      <c r="AJ20" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -3338,7 +3343,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>TWLO</t>
         </is>
@@ -3444,7 +3449,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ21" s="12" t="inlineStr">
+      <c r="AJ21" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -3473,7 +3478,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
@@ -3579,7 +3584,7 @@
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="AJ22" s="12" t="inlineStr">
+      <c r="AJ22" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -3720,7 +3725,7 @@
           <t>2025-08-18</t>
         </is>
       </c>
-      <c r="AJ23" s="12" t="inlineStr">
+      <c r="AJ23" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -3855,7 +3860,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ24" s="12" t="inlineStr">
+      <c r="AJ24" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -3884,7 +3889,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
@@ -3990,7 +3995,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ25" s="12" t="inlineStr">
+      <c r="AJ25" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -4125,7 +4130,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ26" s="12" t="inlineStr">
+      <c r="AJ26" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -4266,7 +4271,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ27" s="12" t="inlineStr">
+      <c r="AJ27" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -4295,7 +4300,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>WPM</t>
         </is>
@@ -4357,7 +4362,7 @@
       <c r="U28" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="11" t="b">
+      <c r="V28" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W28" t="b">
@@ -4401,7 +4406,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ28" s="14" t="inlineStr">
+      <c r="AJ28" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -4536,7 +4541,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ29" s="12" t="inlineStr">
+      <c r="AJ29" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -4671,7 +4676,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ30" s="12" t="inlineStr">
+      <c r="AJ30" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -4817,7 +4822,7 @@
           <t>2025-09-24</t>
         </is>
       </c>
-      <c r="AJ31" s="12" t="inlineStr">
+      <c r="AJ31" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -4952,7 +4957,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ32" s="14" t="inlineStr">
+      <c r="AJ32" s="15" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
@@ -5043,7 +5048,7 @@
       <c r="U33" t="n">
         <v>10.55555555555556</v>
       </c>
-      <c r="V33" s="11" t="b">
+      <c r="V33" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W33" t="b">
@@ -5087,7 +5092,7 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AJ33" s="12" t="inlineStr">
+      <c r="AJ33" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -5151,7 +5156,7 @@
       <c r="K34" t="n">
         <v>1.51</v>
       </c>
-      <c r="L34" s="16" t="n">
+      <c r="L34" s="17" t="n">
         <v>-1.139440324465715</v>
       </c>
       <c r="M34" t="n">
@@ -5178,7 +5183,7 @@
       <c r="U34" t="n">
         <v>12.22222222222222</v>
       </c>
-      <c r="V34" s="11" t="b">
+      <c r="V34" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W34" t="b">
@@ -5222,7 +5227,7 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AJ34" s="14" t="inlineStr">
+      <c r="AJ34" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -5357,7 +5362,7 @@
           <t>2025-07-24</t>
         </is>
       </c>
-      <c r="AJ35" s="12" t="inlineStr">
+      <c r="AJ35" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -5492,7 +5497,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ36" s="12" t="inlineStr">
+      <c r="AJ36" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -5521,7 +5526,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
@@ -5627,7 +5632,7 @@
           <t>2025-07-18</t>
         </is>
       </c>
-      <c r="AJ37" s="12" t="inlineStr">
+      <c r="AJ37" s="13" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -5762,7 +5767,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ38" s="12" t="inlineStr">
+      <c r="AJ38" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -5903,7 +5908,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ39" s="12" t="inlineStr">
+      <c r="AJ39" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -5932,7 +5937,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>BCS</t>
         </is>
@@ -6038,7 +6043,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ40" s="12" t="inlineStr">
+      <c r="AJ40" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -6173,7 +6178,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ41" s="12" t="inlineStr">
+      <c r="AJ41" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -6302,7 +6307,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ42" s="12" t="inlineStr">
+      <c r="AJ42" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -6331,7 +6336,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>SPOT</t>
         </is>
@@ -6437,7 +6442,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ43" s="12" t="inlineStr">
+      <c r="AJ43" s="13" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -6572,7 +6577,7 @@
           <t>2025-07-18</t>
         </is>
       </c>
-      <c r="AJ44" s="12" t="inlineStr">
+      <c r="AJ44" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -6663,7 +6668,7 @@
       <c r="U45" t="n">
         <v>0</v>
       </c>
-      <c r="V45" s="11" t="b">
+      <c r="V45" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W45" t="b">
@@ -6707,7 +6712,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ45" s="12" t="inlineStr">
+      <c r="AJ45" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -6798,7 +6803,7 @@
       <c r="U46" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="V46" s="11" t="b">
+      <c r="V46" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W46" t="b">
@@ -6842,7 +6847,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ46" s="12" t="inlineStr">
+      <c r="AJ46" s="13" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -6983,7 +6988,7 @@
           <t>2025-09-09</t>
         </is>
       </c>
-      <c r="AJ47" s="12" t="inlineStr">
+      <c r="AJ47" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -7012,7 +7017,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="A48" s="14" t="inlineStr">
         <is>
           <t>ULS</t>
         </is>
@@ -7074,7 +7079,7 @@
       <c r="U48" t="n">
         <v>2.222222222222222</v>
       </c>
-      <c r="V48" s="11" t="b">
+      <c r="V48" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W48" t="b">
@@ -7118,7 +7123,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ48" s="12" t="inlineStr">
+      <c r="AJ48" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -7147,7 +7152,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>SRAD</t>
         </is>
@@ -7260,7 +7265,7 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AJ49" s="12" t="inlineStr">
+      <c r="AJ49" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -7348,7 +7353,7 @@
       <c r="S50" t="n">
         <v>1.17</v>
       </c>
-      <c r="T50" s="16" t="inlineStr">
+      <c r="T50" s="17" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
@@ -7403,7 +7408,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ50" s="12" t="inlineStr">
+      <c r="AJ50" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -7432,7 +7437,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="13" t="inlineStr">
+      <c r="A51" s="14" t="inlineStr">
         <is>
           <t>ATRO</t>
         </is>
@@ -7494,7 +7499,7 @@
       <c r="U51" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="V51" s="11" t="b">
+      <c r="V51" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W51" t="b">
@@ -7538,7 +7543,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ51" s="12" t="inlineStr">
+      <c r="AJ51" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -7673,7 +7678,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ52" s="12" t="inlineStr">
+      <c r="AJ52" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -7702,7 +7707,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>TGI</t>
         </is>
@@ -7731,13 +7736,13 @@
       <c r="I53" t="n">
         <v>0.19</v>
       </c>
-      <c r="J53" s="16" t="n">
+      <c r="J53" s="17" t="n">
         <v>-1.390241971161429</v>
       </c>
       <c r="K53" t="n">
         <v>0.52</v>
       </c>
-      <c r="L53" s="16" t="n">
+      <c r="L53" s="17" t="n">
         <v>-1.637022556770439</v>
       </c>
       <c r="M53" t="n">
@@ -7764,7 +7769,7 @@
       <c r="U53" t="n">
         <v>2.777777777777778</v>
       </c>
-      <c r="V53" s="11" t="b">
+      <c r="V53" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W53" t="b">
@@ -7808,7 +7813,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ53" s="12" t="inlineStr">
+      <c r="AJ53" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -7837,7 +7842,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="13" t="inlineStr">
+      <c r="A54" s="14" t="inlineStr">
         <is>
           <t>AVPT</t>
         </is>
@@ -7943,7 +7948,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ54" s="12" t="inlineStr">
+      <c r="AJ54" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -8034,7 +8039,7 @@
       <c r="U55" t="n">
         <v>1.111111111111111</v>
       </c>
-      <c r="V55" s="11" t="b">
+      <c r="V55" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W55" t="b">
@@ -8084,7 +8089,7 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AJ55" s="14" t="inlineStr">
+      <c r="AJ55" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -8113,7 +8118,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>SEZL</t>
         </is>
@@ -8219,7 +8224,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ56" s="12" t="inlineStr">
+      <c r="AJ56" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -8248,7 +8253,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>CALM</t>
         </is>
@@ -8310,7 +8315,7 @@
       <c r="U57" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="11" t="b">
+      <c r="V57" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W57" t="b">
@@ -8354,7 +8359,7 @@
           <t>2025-07-21</t>
         </is>
       </c>
-      <c r="AJ57" s="14" t="inlineStr">
+      <c r="AJ57" s="15" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -8489,7 +8494,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ58" s="12" t="inlineStr">
+      <c r="AJ58" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -8518,7 +8523,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="14" t="inlineStr">
         <is>
           <t>MVST</t>
         </is>
@@ -8624,7 +8629,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ59" s="12" t="inlineStr">
+      <c r="AJ59" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -8759,7 +8764,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ60" s="14" t="inlineStr">
+      <c r="AJ60" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -8894,7 +8899,7 @@
           <t>2025-08-19</t>
         </is>
       </c>
-      <c r="AJ61" s="12" t="inlineStr">
+      <c r="AJ61" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -8923,7 +8928,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>ROAD</t>
         </is>
@@ -9029,7 +9034,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ62" s="12" t="inlineStr">
+      <c r="AJ62" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -9164,7 +9169,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ63" s="12" t="inlineStr">
+      <c r="AJ63" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -9193,7 +9198,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>IDT</t>
         </is>
@@ -9304,7 +9309,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AJ64" s="12" t="inlineStr">
+      <c r="AJ64" s="13" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -9439,7 +9444,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ65" s="12" t="inlineStr">
+      <c r="AJ65" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -9574,7 +9579,7 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AJ66" s="12" t="inlineStr">
+      <c r="AJ66" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -9709,7 +9714,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ67" s="12" t="inlineStr">
+      <c r="AJ67" s="13" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -9767,13 +9772,13 @@
       <c r="I68" t="n">
         <v>10.36</v>
       </c>
-      <c r="J68" s="13" t="n">
+      <c r="J68" s="14" t="n">
         <v>3.612913012313577</v>
       </c>
       <c r="K68" t="n">
         <v>9.42</v>
       </c>
-      <c r="L68" s="13" t="n">
+      <c r="L68" s="14" t="n">
         <v>2.836191450817482</v>
       </c>
       <c r="M68" t="n">
@@ -9850,7 +9855,7 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AJ68" s="12" t="inlineStr">
+      <c r="AJ68" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -9879,7 +9884,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
@@ -9988,7 +9993,7 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AJ69" s="12" t="inlineStr">
+      <c r="AJ69" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -10126,7 +10131,7 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AJ70" s="14" t="inlineStr">
+      <c r="AJ70" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -10261,7 +10266,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ71" s="12" t="inlineStr">
+      <c r="AJ71" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -10319,13 +10324,13 @@
       <c r="I72" t="n">
         <v>10.48</v>
       </c>
-      <c r="J72" s="13" t="n">
+      <c r="J72" s="14" t="n">
         <v>3.671947289404728</v>
       </c>
       <c r="K72" t="n">
         <v>11.8</v>
       </c>
-      <c r="L72" s="13" t="n">
+      <c r="L72" s="14" t="n">
         <v>4.032399241610658</v>
       </c>
       <c r="M72" t="n">
@@ -10402,7 +10407,7 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AJ72" s="14" t="inlineStr">
+      <c r="AJ72" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -10431,7 +10436,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>RDWR</t>
         </is>
@@ -10490,7 +10495,7 @@
       <c r="S73" t="n">
         <v>1.09</v>
       </c>
-      <c r="T73" s="16" t="inlineStr">
+      <c r="T73" s="17" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
@@ -10548,7 +10553,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ73" s="12" t="inlineStr">
+      <c r="AJ73" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -10577,7 +10582,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>IFS</t>
         </is>
@@ -10677,7 +10682,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ74" s="12" t="inlineStr">
+      <c r="AJ74" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -10706,7 +10711,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>EAT</t>
         </is>
@@ -10768,7 +10773,7 @@
       <c r="U75" t="n">
         <v>0</v>
       </c>
-      <c r="V75" s="11" t="b">
+      <c r="V75" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W75" t="b">
@@ -10812,7 +10817,7 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AJ75" s="12" t="inlineStr">
+      <c r="AJ75" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -10841,7 +10846,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="13" t="inlineStr">
+      <c r="A76" s="14" t="inlineStr">
         <is>
           <t>BTSG</t>
         </is>
@@ -10947,7 +10952,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ76" s="14" t="inlineStr">
+      <c r="AJ76" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -10976,7 +10981,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="13" t="inlineStr">
+      <c r="A77" s="14" t="inlineStr">
         <is>
           <t>MRCY</t>
         </is>
@@ -11082,7 +11087,7 @@
           <t>2025-08-13</t>
         </is>
       </c>
-      <c r="AJ77" s="12" t="inlineStr">
+      <c r="AJ77" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -11146,7 +11151,7 @@
       <c r="K78" t="n">
         <v>10.15</v>
       </c>
-      <c r="L78" s="13" t="n">
+      <c r="L78" s="14" t="n">
         <v>3.203095521102784</v>
       </c>
       <c r="M78" t="n">
@@ -11217,7 +11222,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ78" s="12" t="inlineStr">
+      <c r="AJ78" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -11246,7 +11251,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="13" t="inlineStr">
+      <c r="A79" s="14" t="inlineStr">
         <is>
           <t>VRNA</t>
         </is>
@@ -11352,7 +11357,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ79" s="14" t="inlineStr">
+      <c r="AJ79" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -11487,7 +11492,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ80" s="12" t="inlineStr">
+      <c r="AJ80" s="13" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -11516,7 +11521,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>PAHC</t>
         </is>
@@ -11628,7 +11633,7 @@
           <t>2025-08-28</t>
         </is>
       </c>
-      <c r="AJ81" s="14" t="inlineStr">
+      <c r="AJ81" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -11657,7 +11662,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="13" t="inlineStr">
+      <c r="A82" s="14" t="inlineStr">
         <is>
           <t>TRUP</t>
         </is>
@@ -11769,7 +11774,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ82" s="12" t="inlineStr">
+      <c r="AJ82" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -11904,7 +11909,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ83" s="12" t="inlineStr">
+      <c r="AJ83" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -12039,7 +12044,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ84" s="12" t="inlineStr">
+      <c r="AJ84" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -12130,7 +12135,7 @@
       <c r="U85" t="n">
         <v>0</v>
       </c>
-      <c r="V85" s="11" t="b">
+      <c r="V85" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W85" t="b">
@@ -12174,7 +12179,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ85" s="14" t="inlineStr">
+      <c r="AJ85" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -12203,7 +12208,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="13" t="inlineStr">
+      <c r="A86" s="14" t="inlineStr">
         <is>
           <t>SMR</t>
         </is>
@@ -12232,7 +12237,7 @@
       <c r="I86" t="n">
         <v>8.210000000000001</v>
       </c>
-      <c r="J86" s="13" t="n">
+      <c r="J86" s="14" t="n">
         <v>2.555215547763797</v>
       </c>
       <c r="K86" t="n">
@@ -12309,7 +12314,7 @@
           <t>2025-08-08</t>
         </is>
       </c>
-      <c r="AJ86" s="12" t="inlineStr">
+      <c r="AJ86" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -12450,7 +12455,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ87" s="12" t="inlineStr">
+      <c r="AJ87" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -12585,7 +12590,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ88" s="14" t="inlineStr">
+      <c r="AJ88" s="15" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -12720,7 +12725,7 @@
           <t>2025-07-29</t>
         </is>
       </c>
-      <c r="AJ89" s="12" t="inlineStr">
+      <c r="AJ89" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -12749,7 +12754,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="13" t="inlineStr">
+      <c r="A90" s="14" t="inlineStr">
         <is>
           <t>OR</t>
         </is>
@@ -12811,7 +12816,7 @@
       <c r="U90" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="11" t="b">
+      <c r="V90" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W90" t="b">
@@ -12855,7 +12860,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ90" s="14" t="inlineStr">
+      <c r="AJ90" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -12919,7 +12924,7 @@
       <c r="K91" t="n">
         <v>9.6</v>
       </c>
-      <c r="L91" s="13" t="n">
+      <c r="L91" s="14" t="n">
         <v>2.926660947600159</v>
       </c>
       <c r="M91" t="n">
@@ -12990,7 +12995,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ91" s="12" t="inlineStr">
+      <c r="AJ91" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -13019,7 +13024,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="13" t="inlineStr">
+      <c r="A92" s="16" t="inlineStr">
         <is>
           <t>AGX</t>
         </is>
@@ -13125,7 +13130,7 @@
           <t>2025-09-05</t>
         </is>
       </c>
-      <c r="AJ92" s="12" t="inlineStr">
+      <c r="AJ92" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -13266,7 +13271,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ93" s="12" t="inlineStr">
+      <c r="AJ93" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -13407,7 +13412,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ94" s="12" t="inlineStr">
+      <c r="AJ94" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -13542,7 +13547,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ95" s="14" t="inlineStr">
+      <c r="AJ95" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -13571,7 +13576,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
+      <c r="A96" s="11" t="inlineStr">
         <is>
           <t>MAG</t>
         </is>
@@ -13633,7 +13638,7 @@
       <c r="U96" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="11" t="b">
+      <c r="V96" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W96" t="b">
@@ -13677,7 +13682,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ96" s="14" t="inlineStr">
+      <c r="AJ96" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -13706,7 +13711,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>REVG</t>
         </is>
@@ -13812,7 +13817,7 @@
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="AJ97" s="12" t="inlineStr">
+      <c r="AJ97" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -13841,7 +13846,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="13" t="inlineStr">
+      <c r="A98" s="14" t="inlineStr">
         <is>
           <t>SITM</t>
         </is>
@@ -13953,7 +13958,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ98" s="12" t="inlineStr">
+      <c r="AJ98" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -14088,7 +14093,7 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AJ99" s="12" t="inlineStr">
+      <c r="AJ99" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -14146,7 +14151,7 @@
       <c r="I100" t="n">
         <v>11.58</v>
       </c>
-      <c r="J100" s="13" t="n">
+      <c r="J100" s="14" t="n">
         <v>4.21309482940694</v>
       </c>
       <c r="K100" t="n">
@@ -14223,7 +14228,7 @@
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="AJ100" s="12" t="inlineStr">
+      <c r="AJ100" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -14364,7 +14369,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ101" s="12" t="inlineStr">
+      <c r="AJ101" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -14505,7 +14510,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ102" s="12" t="inlineStr">
+      <c r="AJ102" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -14640,7 +14645,7 @@
           <t>2025-08-27</t>
         </is>
       </c>
-      <c r="AJ103" s="12" t="inlineStr">
+      <c r="AJ103" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -14669,7 +14674,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="13" t="inlineStr">
+      <c r="A104" s="14" t="inlineStr">
         <is>
           <t>TPB</t>
         </is>
@@ -14731,7 +14736,7 @@
       <c r="U104" t="n">
         <v>6.111111111111111</v>
       </c>
-      <c r="V104" s="11" t="b">
+      <c r="V104" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W104" t="b">
@@ -14775,7 +14780,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ104" s="14" t="inlineStr">
+      <c r="AJ104" s="15" t="inlineStr">
         <is>
           <t>Consumer Defensive</t>
         </is>
@@ -14804,7 +14809,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="13" t="inlineStr">
+      <c r="A105" s="14" t="inlineStr">
         <is>
           <t>QFIN</t>
         </is>
@@ -14910,7 +14915,7 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AJ105" s="12" t="inlineStr">
+      <c r="AJ105" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -15045,7 +15050,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ106" s="12" t="inlineStr">
+      <c r="AJ106" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -15074,7 +15079,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>VIRT</t>
         </is>
@@ -15180,7 +15185,7 @@
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="AJ107" s="12" t="inlineStr">
+      <c r="AJ107" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -15318,7 +15323,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ108" s="12" t="inlineStr">
+      <c r="AJ108" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -15456,7 +15461,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ109" s="12" t="inlineStr">
+      <c r="AJ109" s="13" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
@@ -15591,7 +15596,7 @@
           <t>2025-08-09</t>
         </is>
       </c>
-      <c r="AJ110" s="12" t="inlineStr">
+      <c r="AJ110" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -15726,7 +15731,7 @@
           <t>2025-08-21</t>
         </is>
       </c>
-      <c r="AJ111" s="12" t="inlineStr">
+      <c r="AJ111" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -15861,7 +15866,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ112" s="12" t="inlineStr">
+      <c r="AJ112" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -15996,7 +16001,7 @@
           <t>2025-08-04</t>
         </is>
       </c>
-      <c r="AJ113" s="12" t="inlineStr">
+      <c r="AJ113" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -16025,7 +16030,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
+      <c r="A114" s="11" t="inlineStr">
         <is>
           <t>PSIX</t>
         </is>
@@ -16131,7 +16136,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ114" s="12" t="inlineStr">
+      <c r="AJ114" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -16266,7 +16271,7 @@
           <t>2025-08-01</t>
         </is>
       </c>
-      <c r="AJ115" s="14" t="inlineStr">
+      <c r="AJ115" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -16295,7 +16300,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="13" t="inlineStr">
+      <c r="A116" s="14" t="inlineStr">
         <is>
           <t>ZLAB</t>
         </is>
@@ -16401,7 +16406,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ116" s="14" t="inlineStr">
+      <c r="AJ116" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -16459,7 +16464,7 @@
       <c r="I117" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J117" s="13" t="n">
+      <c r="J117" s="14" t="n">
         <v>2.59949125558216</v>
       </c>
       <c r="K117" t="n">
@@ -16542,7 +16547,7 @@
           <t>2025-08-11</t>
         </is>
       </c>
-      <c r="AJ117" s="12" t="inlineStr">
+      <c r="AJ117" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -16683,7 +16688,7 @@
           <t>2025-08-07</t>
         </is>
       </c>
-      <c r="AJ118" s="12" t="inlineStr">
+      <c r="AJ118" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -16818,7 +16823,7 @@
           <t>2025-07-28</t>
         </is>
       </c>
-      <c r="AJ119" s="12" t="inlineStr">
+      <c r="AJ119" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -16876,13 +16881,13 @@
       <c r="I120" t="n">
         <v>10.15</v>
       </c>
-      <c r="J120" s="13" t="n">
+      <c r="J120" s="14" t="n">
         <v>3.509603027404064</v>
       </c>
       <c r="K120" t="n">
         <v>11.55</v>
       </c>
-      <c r="L120" s="13" t="n">
+      <c r="L120" s="14" t="n">
         <v>3.906747162745828</v>
       </c>
       <c r="M120" t="n">
@@ -16953,7 +16958,7 @@
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="AJ120" s="14" t="inlineStr">
+      <c r="AJ120" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -17088,7 +17093,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ121" s="14" t="inlineStr">
+      <c r="AJ121" s="15" t="inlineStr">
         <is>
           <t>Healthcare</t>
         </is>
@@ -17223,7 +17228,7 @@
           <t>2025-08-20</t>
         </is>
       </c>
-      <c r="AJ122" s="12" t="inlineStr">
+      <c r="AJ122" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -17252,7 +17257,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>LMB</t>
         </is>
@@ -17358,7 +17363,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ123" s="12" t="inlineStr">
+      <c r="AJ123" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -17493,7 +17498,7 @@
           <t>2025-08-06</t>
         </is>
       </c>
-      <c r="AJ124" s="12" t="inlineStr">
+      <c r="AJ124" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -17628,7 +17633,7 @@
           <t>2025-07-23</t>
         </is>
       </c>
-      <c r="AJ125" s="12" t="inlineStr">
+      <c r="AJ125" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -17763,7 +17768,7 @@
           <t>2025-07-22</t>
         </is>
       </c>
-      <c r="AJ126" s="12" t="inlineStr">
+      <c r="AJ126" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
@@ -17821,13 +17826,13 @@
       <c r="I127" t="n">
         <v>8.81</v>
       </c>
-      <c r="J127" s="13" t="n">
+      <c r="J127" s="14" t="n">
         <v>2.85038693321955</v>
       </c>
       <c r="K127" t="n">
         <v>8.630000000000001</v>
       </c>
-      <c r="L127" s="13" t="n">
+      <c r="L127" s="14" t="n">
         <v>2.439130881604622</v>
       </c>
       <c r="M127" t="n">
@@ -17898,7 +17903,7 @@
           <t>2025-08-05</t>
         </is>
       </c>
-      <c r="AJ127" s="12" t="inlineStr">
+      <c r="AJ127" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
@@ -18033,7 +18038,7 @@
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="AJ128" s="14" t="inlineStr">
+      <c r="AJ128" s="15" t="inlineStr">
         <is>
           <t>Basic Materials</t>
         </is>
@@ -18124,7 +18129,7 @@
       <c r="U129" t="n">
         <v>0</v>
       </c>
-      <c r="V129" s="11" t="b">
+      <c r="V129" s="12" t="b">
         <v>1</v>
       </c>
       <c r="W129" t="b">
@@ -18174,7 +18179,7 @@
           <t>2025-07-30</t>
         </is>
       </c>
-      <c r="AJ129" s="12" t="inlineStr">
+      <c r="AJ129" s="13" t="inlineStr">
         <is>
           <t>Consumer Cyclical</t>
         </is>
@@ -18262,7 +18267,7 @@
       <c r="S130" t="n">
         <v>1.15</v>
       </c>
-      <c r="T130" s="16" t="inlineStr">
+      <c r="T130" s="17" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
@@ -18317,7 +18322,7 @@
           <t>2025-08-12</t>
         </is>
       </c>
-      <c r="AJ130" s="12" t="inlineStr">
+      <c r="AJ130" s="13" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
